--- a/Tuan 5/Buoi 1/LED7DOAN_74HC595/HDLapBangMaLED7Doan.xlsx
+++ b/Tuan 5/Buoi 1/LED7DOAN_74HC595/HDLapBangMaLED7Doan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\VXL_VDK_STM32\Tuan 5\Buoi 1\LED7DOAN_74HC595\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E24ABF-A3A1-49D1-A090-7D8BAA92B3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B90C8C-8247-4681-8682-FD72D9038A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{262ADE5C-7A4A-4646-9063-ED7C8D1A9836}"/>
   </bookViews>
@@ -455,15 +455,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>447840</xdr:colOff>
+      <xdr:colOff>420946</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>68400</xdr:rowOff>
+      <xdr:rowOff>50471</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>253920</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>300</xdr:rowOff>
+      <xdr:colOff>227026</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>161665</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
       <mc:Choice Requires="xdr14">
@@ -480,8 +480,8 @@
           </xdr14:nvContentPartPr>
           <xdr14:nvPr macro=""/>
           <xdr14:xfrm>
-            <a:off x="447840" y="1348560"/>
-            <a:ext cx="2122560" cy="3048480"/>
+            <a:off x="420946" y="1314495"/>
+            <a:ext cx="2118974" cy="2988864"/>
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
